--- a/InputData/web-app/BCF/BTU Conversion Factors.xlsx
+++ b/InputData/web-app/BCF/BTU Conversion Factors.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28429"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Olivia Ashmoore\Documents\EPS_Models by Region\United States\us-eps\InputData\web-app\BCF\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\kjh_local\NEXTgroup_local\2025_local\2. EPS\eps-us-main\InputData\web-app\BCF\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{164845E5-F203-493C-B648-3ABC9D0083FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0EA96575-CED4-438D-A939-097017A30AB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="130" yWindow="0" windowWidth="17840" windowHeight="10080" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3915" yWindow="4560" windowWidth="12675" windowHeight="8400" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -2494,33 +2494,33 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
   <numFmts count="14">
-    <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="164" formatCode="0.0%"/>
-    <numFmt numFmtId="165" formatCode="0.000E+00"/>
-    <numFmt numFmtId="166" formatCode="#,##0.000"/>
-    <numFmt numFmtId="167" formatCode="0.000"/>
-    <numFmt numFmtId="168" formatCode="#,##0.000000"/>
-    <numFmt numFmtId="169" formatCode="#,##0.0"/>
-    <numFmt numFmtId="170" formatCode="0.000000"/>
-    <numFmt numFmtId="171" formatCode="0.0"/>
-    <numFmt numFmtId="172" formatCode="0.0000"/>
-    <numFmt numFmtId="173" formatCode="#,##0.0000"/>
-    <numFmt numFmtId="174" formatCode="#,##0.000000000"/>
-    <numFmt numFmtId="175" formatCode="#,##0.0000000000"/>
-    <numFmt numFmtId="176" formatCode="#,##0.0000000"/>
+    <numFmt numFmtId="176" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="177" formatCode="0.0%"/>
+    <numFmt numFmtId="178" formatCode="0.000E+00"/>
+    <numFmt numFmtId="179" formatCode="#,##0.000"/>
+    <numFmt numFmtId="180" formatCode="0.000"/>
+    <numFmt numFmtId="181" formatCode="#,##0.000000"/>
+    <numFmt numFmtId="182" formatCode="#,##0.0"/>
+    <numFmt numFmtId="183" formatCode="0.000000"/>
+    <numFmt numFmtId="184" formatCode="0.0"/>
+    <numFmt numFmtId="185" formatCode="0.0000"/>
+    <numFmt numFmtId="186" formatCode="#,##0.0000"/>
+    <numFmt numFmtId="187" formatCode="#,##0.000000000"/>
+    <numFmt numFmtId="188" formatCode="#,##0.0000000000"/>
+    <numFmt numFmtId="189" formatCode="#,##0.0000000"/>
   </numFmts>
-  <fonts count="40" x14ac:knownFonts="1">
+  <fonts count="41" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -2528,7 +2528,7 @@
       <b/>
       <sz val="18"/>
       <color theme="3"/>
-      <name val="Cambria"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="major"/>
     </font>
@@ -2536,7 +2536,7 @@
       <b/>
       <sz val="15"/>
       <color theme="3"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -2544,7 +2544,7 @@
       <b/>
       <sz val="13"/>
       <color theme="3"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -2552,35 +2552,35 @@
       <b/>
       <sz val="11"/>
       <color theme="3"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF006100"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF9C0006"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF9C6500"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF3F3F76"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -2588,7 +2588,7 @@
       <b/>
       <sz val="11"/>
       <color rgb="FF3F3F3F"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -2596,14 +2596,14 @@
       <b/>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -2611,14 +2611,14 @@
       <b/>
       <sz val="11"/>
       <color theme="0"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -2626,7 +2626,7 @@
       <i/>
       <sz val="11"/>
       <color rgb="FF7F7F7F"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -2634,14 +2634,14 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="0"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -2649,14 +2649,14 @@
       <b/>
       <sz val="9"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="9"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -2664,7 +2664,7 @@
       <u/>
       <sz val="10"/>
       <color theme="4"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -2679,7 +2679,7 @@
       <b/>
       <sz val="12"/>
       <color theme="4"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -2687,7 +2687,7 @@
       <u/>
       <sz val="11"/>
       <color rgb="FF0070C0"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -2785,8 +2785,15 @@
       <i/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -3516,7 +3523,7 @@
     <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyNumberFormat="0" applyProtection="0">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="184">
@@ -3526,11 +3533,11 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="47" applyFont="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="54"/>
     <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="54" applyFont="1"/>
     <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="54" applyFont="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="18" xfId="57" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="18" xfId="57" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="18" xfId="57" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -3542,7 +3549,7 @@
     <xf numFmtId="0" fontId="26" fillId="0" borderId="17" xfId="56">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="18" xfId="57" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="18" xfId="57" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="17" xfId="56" applyFont="1">
@@ -3573,7 +3580,7 @@
     <xf numFmtId="0" fontId="32" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="167" fontId="32" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="180" fontId="32" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="32" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -3588,14 +3595,14 @@
     <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="32" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="180" fontId="32" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="32" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="32" fillId="33" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="167" fontId="32" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="180" fontId="32" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="32" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="32" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -3604,77 +3611,77 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="32" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="32" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="180" fontId="32" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="33" fillId="0" borderId="23" xfId="61" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="3" fontId="33" fillId="34" borderId="0" xfId="61" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="164" fontId="33" fillId="34" borderId="0" xfId="62" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="177" fontId="33" fillId="34" borderId="0" xfId="62" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="3" fontId="33" fillId="35" borderId="0" xfId="61" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="168" fontId="33" fillId="0" borderId="0" xfId="61" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="167" fontId="33" fillId="0" borderId="24" xfId="61" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="181" fontId="33" fillId="0" borderId="0" xfId="61" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="180" fontId="33" fillId="0" borderId="24" xfId="61" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="3" fontId="33" fillId="36" borderId="0" xfId="61" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="164" fontId="33" fillId="36" borderId="0" xfId="62" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="177" fontId="33" fillId="36" borderId="0" xfId="62" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="3" fontId="33" fillId="0" borderId="0" xfId="61" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="164" fontId="33" fillId="0" borderId="0" xfId="62" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="167" fontId="33" fillId="0" borderId="0" xfId="61" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="177" fontId="33" fillId="0" borderId="0" xfId="62" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="180" fontId="33" fillId="0" borderId="0" xfId="61" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="33" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="37" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="1" fontId="33" fillId="0" borderId="0" xfId="62" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="33" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="33" fillId="0" borderId="0" xfId="61" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="177" fontId="33" fillId="0" borderId="0" xfId="61" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="3" fontId="33" fillId="38" borderId="0" xfId="61" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="164" fontId="33" fillId="35" borderId="0" xfId="62" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="177" fontId="33" fillId="35" borderId="0" xfId="62" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="3" fontId="0" fillId="38" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="164" fontId="0" fillId="38" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="164" fontId="33" fillId="38" borderId="0" xfId="62" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="177" fontId="0" fillId="38" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="177" fontId="33" fillId="38" borderId="0" xfId="62" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="3" fontId="33" fillId="0" borderId="0" xfId="62" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="3" fontId="33" fillId="0" borderId="0" xfId="61" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="164" fontId="33" fillId="0" borderId="0" xfId="62" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="177" fontId="33" fillId="0" borderId="0" xfId="62" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="3" fontId="32" fillId="0" borderId="25" xfId="61" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="3" fontId="32" fillId="0" borderId="26" xfId="61" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="32" fillId="0" borderId="26" xfId="62" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="177" fontId="32" fillId="0" borderId="26" xfId="62" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="3" fontId="32" fillId="0" borderId="26" xfId="61" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="168" fontId="32" fillId="0" borderId="26" xfId="61" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="167" fontId="32" fillId="0" borderId="27" xfId="61" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="169" fontId="33" fillId="34" borderId="0" xfId="61" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="181" fontId="32" fillId="0" borderId="26" xfId="61" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="180" fontId="32" fillId="0" borderId="27" xfId="61" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="182" fontId="33" fillId="34" borderId="0" xfId="61" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="3" fontId="33" fillId="39" borderId="0" xfId="61" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="169" fontId="33" fillId="39" borderId="0" xfId="61" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="169" fontId="33" fillId="38" borderId="0" xfId="61" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="169" fontId="33" fillId="36" borderId="0" xfId="61" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="182" fontId="33" fillId="39" borderId="0" xfId="61" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="182" fontId="33" fillId="38" borderId="0" xfId="61" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="182" fontId="33" fillId="36" borderId="0" xfId="61" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="3" fontId="32" fillId="0" borderId="26" xfId="61" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="167" fontId="33" fillId="38" borderId="24" xfId="61" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="180" fontId="33" fillId="38" borderId="24" xfId="61" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="33" fillId="40" borderId="0" xfId="61" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="62" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="170" fontId="33" fillId="0" borderId="0" xfId="61" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="164" fontId="33" fillId="35" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="183" fontId="33" fillId="0" borderId="0" xfId="61" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="177" fontId="33" fillId="35" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="181" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="180" fontId="0" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="33" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="33" fillId="38" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="164" fontId="33" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="177" fontId="33" fillId="38" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="177" fontId="33" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="33" fillId="0" borderId="30" xfId="61" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="3" fontId="33" fillId="38" borderId="30" xfId="61" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="164" fontId="33" fillId="38" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="31" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="177" fontId="33" fillId="38" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="181" fontId="0" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="180" fontId="0" fillId="0" borderId="31" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="61" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="61" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="62" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="62" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="180" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="61" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -3740,19 +3747,19 @@
     <xf numFmtId="0" fontId="0" fillId="35" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="171" fontId="0" fillId="35" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="184" fontId="0" fillId="35" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="169" fontId="0" fillId="35" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="182" fontId="0" fillId="35" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="171" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="184" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="182" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="32" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -3770,34 +3777,34 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="182" fontId="0" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="32" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="169" fontId="32" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="182" fontId="32" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="32" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="32" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="182" fontId="0" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="31" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="31" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="32" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -3815,52 +3822,52 @@
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="181" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="181" fontId="0" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="31" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="183" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="180" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="172" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="185" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="172" fontId="0" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="185" fontId="0" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="173" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="186" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="174" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="187" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="175" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="188" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="189" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="42" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -3871,7 +3878,7 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="42" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="38" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="164" fontId="26" fillId="0" borderId="17" xfId="56" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="26" fillId="0" borderId="17" xfId="56" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
     <xf numFmtId="3" fontId="26" fillId="0" borderId="17" xfId="56" applyNumberFormat="1" applyAlignment="1">
@@ -3884,69 +3891,69 @@
     </xf>
   </cellXfs>
   <cellStyles count="63">
-    <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
-    <cellStyle name="20% - Accent2" xfId="23" builtinId="34" customBuiltin="1"/>
-    <cellStyle name="20% - Accent3" xfId="27" builtinId="38" customBuiltin="1"/>
-    <cellStyle name="20% - Accent4" xfId="31" builtinId="42" customBuiltin="1"/>
-    <cellStyle name="20% - Accent5" xfId="35" builtinId="46" customBuiltin="1"/>
-    <cellStyle name="20% - Accent6" xfId="39" builtinId="50" customBuiltin="1"/>
-    <cellStyle name="40% - Accent1" xfId="20" builtinId="31" customBuiltin="1"/>
-    <cellStyle name="40% - Accent2" xfId="24" builtinId="35" customBuiltin="1"/>
-    <cellStyle name="40% - Accent3" xfId="28" builtinId="39" customBuiltin="1"/>
-    <cellStyle name="40% - Accent4" xfId="32" builtinId="43" customBuiltin="1"/>
-    <cellStyle name="40% - Accent5" xfId="36" builtinId="47" customBuiltin="1"/>
-    <cellStyle name="40% - Accent6" xfId="40" builtinId="51" customBuiltin="1"/>
-    <cellStyle name="60% - Accent1" xfId="21" builtinId="32" customBuiltin="1"/>
-    <cellStyle name="60% - Accent2" xfId="25" builtinId="36" customBuiltin="1"/>
-    <cellStyle name="60% - Accent3" xfId="29" builtinId="40" customBuiltin="1"/>
-    <cellStyle name="60% - Accent4" xfId="33" builtinId="44" customBuiltin="1"/>
-    <cellStyle name="60% - Accent5" xfId="37" builtinId="48" customBuiltin="1"/>
-    <cellStyle name="60% - Accent6" xfId="41" builtinId="52" customBuiltin="1"/>
-    <cellStyle name="Accent1" xfId="18" builtinId="29" customBuiltin="1"/>
-    <cellStyle name="Accent2" xfId="22" builtinId="33" customBuiltin="1"/>
-    <cellStyle name="Accent3" xfId="26" builtinId="37" customBuiltin="1"/>
-    <cellStyle name="Accent4" xfId="30" builtinId="41" customBuiltin="1"/>
-    <cellStyle name="Accent5" xfId="34" builtinId="45" customBuiltin="1"/>
-    <cellStyle name="Accent6" xfId="38" builtinId="49" customBuiltin="1"/>
-    <cellStyle name="Bad" xfId="7" builtinId="27" customBuiltin="1"/>
+    <cellStyle name="20% - 강조색1" xfId="19" builtinId="30" customBuiltin="1"/>
+    <cellStyle name="20% - 강조색2" xfId="23" builtinId="34" customBuiltin="1"/>
+    <cellStyle name="20% - 강조색3" xfId="27" builtinId="38" customBuiltin="1"/>
+    <cellStyle name="20% - 강조색4" xfId="31" builtinId="42" customBuiltin="1"/>
+    <cellStyle name="20% - 강조색5" xfId="35" builtinId="46" customBuiltin="1"/>
+    <cellStyle name="20% - 강조색6" xfId="39" builtinId="50" customBuiltin="1"/>
+    <cellStyle name="40% - 강조색1" xfId="20" builtinId="31" customBuiltin="1"/>
+    <cellStyle name="40% - 강조색2" xfId="24" builtinId="35" customBuiltin="1"/>
+    <cellStyle name="40% - 강조색3" xfId="28" builtinId="39" customBuiltin="1"/>
+    <cellStyle name="40% - 강조색4" xfId="32" builtinId="43" customBuiltin="1"/>
+    <cellStyle name="40% - 강조색5" xfId="36" builtinId="47" customBuiltin="1"/>
+    <cellStyle name="40% - 강조색6" xfId="40" builtinId="51" customBuiltin="1"/>
+    <cellStyle name="60% - 강조색1" xfId="21" builtinId="32" customBuiltin="1"/>
+    <cellStyle name="60% - 강조색2" xfId="25" builtinId="36" customBuiltin="1"/>
+    <cellStyle name="60% - 강조색3" xfId="29" builtinId="40" customBuiltin="1"/>
+    <cellStyle name="60% - 강조색4" xfId="33" builtinId="44" customBuiltin="1"/>
+    <cellStyle name="60% - 강조색5" xfId="37" builtinId="48" customBuiltin="1"/>
+    <cellStyle name="60% - 강조색6" xfId="41" builtinId="52" customBuiltin="1"/>
     <cellStyle name="Body: normal cell" xfId="48" xr:uid="{00000000-0005-0000-0000-000019000000}"/>
     <cellStyle name="Body: normal cell 2" xfId="57" xr:uid="{00000000-0005-0000-0000-00001A000000}"/>
-    <cellStyle name="Calculation" xfId="11" builtinId="22" customBuiltin="1"/>
-    <cellStyle name="Check Cell" xfId="13" builtinId="23" customBuiltin="1"/>
-    <cellStyle name="Comma" xfId="61" builtinId="3"/>
-    <cellStyle name="Explanatory Text" xfId="16" builtinId="53" customBuiltin="1"/>
-    <cellStyle name="Followed Hyperlink" xfId="53" builtinId="9" customBuiltin="1"/>
     <cellStyle name="Font: Calibri, 9pt regular" xfId="43" xr:uid="{00000000-0005-0000-0000-000020000000}"/>
     <cellStyle name="Font: Calibri, 9pt regular 2" xfId="59" xr:uid="{00000000-0005-0000-0000-000021000000}"/>
     <cellStyle name="Footnotes: all except top row" xfId="52" xr:uid="{00000000-0005-0000-0000-000022000000}"/>
     <cellStyle name="Footnotes: top row" xfId="45" xr:uid="{00000000-0005-0000-0000-000023000000}"/>
     <cellStyle name="Footnotes: top row 2" xfId="55" xr:uid="{00000000-0005-0000-0000-000024000000}"/>
-    <cellStyle name="Good" xfId="6" builtinId="26" customBuiltin="1"/>
     <cellStyle name="Header: bottom row" xfId="42" xr:uid="{00000000-0005-0000-0000-000026000000}"/>
     <cellStyle name="Header: bottom row 2" xfId="58" xr:uid="{00000000-0005-0000-0000-000027000000}"/>
     <cellStyle name="Header: top rows" xfId="51" xr:uid="{00000000-0005-0000-0000-000028000000}"/>
-    <cellStyle name="Heading 1" xfId="2" builtinId="16" customBuiltin="1"/>
-    <cellStyle name="Heading 2" xfId="3" builtinId="17" customBuiltin="1"/>
-    <cellStyle name="Heading 3" xfId="4" builtinId="18" customBuiltin="1"/>
-    <cellStyle name="Heading 4" xfId="5" builtinId="19" customBuiltin="1"/>
-    <cellStyle name="Hyperlink" xfId="47" builtinId="8" customBuiltin="1"/>
-    <cellStyle name="Input" xfId="9" builtinId="20" customBuiltin="1"/>
-    <cellStyle name="Linked Cell" xfId="12" builtinId="24" customBuiltin="1"/>
-    <cellStyle name="Neutral" xfId="8" builtinId="28" customBuiltin="1"/>
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="54" xr:uid="{00000000-0005-0000-0000-000032000000}"/>
-    <cellStyle name="Note" xfId="15" builtinId="10" customBuiltin="1"/>
-    <cellStyle name="Output" xfId="10" builtinId="21" customBuiltin="1"/>
     <cellStyle name="Parent row" xfId="46" xr:uid="{00000000-0005-0000-0000-000035000000}"/>
     <cellStyle name="Parent row 2" xfId="56" xr:uid="{00000000-0005-0000-0000-000036000000}"/>
-    <cellStyle name="Percent" xfId="62" builtinId="5"/>
     <cellStyle name="Section Break" xfId="44" xr:uid="{00000000-0005-0000-0000-000038000000}"/>
     <cellStyle name="Section Break: parent row" xfId="49" xr:uid="{00000000-0005-0000-0000-000039000000}"/>
     <cellStyle name="Table title" xfId="50" xr:uid="{00000000-0005-0000-0000-00003A000000}"/>
     <cellStyle name="Table title 2" xfId="60" xr:uid="{00000000-0005-0000-0000-00003B000000}"/>
-    <cellStyle name="Title" xfId="1" builtinId="15" customBuiltin="1"/>
-    <cellStyle name="Total" xfId="17" builtinId="25" customBuiltin="1"/>
-    <cellStyle name="Warning Text" xfId="14" builtinId="11" customBuiltin="1"/>
+    <cellStyle name="강조색1" xfId="18" builtinId="29" customBuiltin="1"/>
+    <cellStyle name="강조색2" xfId="22" builtinId="33" customBuiltin="1"/>
+    <cellStyle name="강조색3" xfId="26" builtinId="37" customBuiltin="1"/>
+    <cellStyle name="강조색4" xfId="30" builtinId="41" customBuiltin="1"/>
+    <cellStyle name="강조색5" xfId="34" builtinId="45" customBuiltin="1"/>
+    <cellStyle name="강조색6" xfId="38" builtinId="49" customBuiltin="1"/>
+    <cellStyle name="경고문" xfId="14" builtinId="11" customBuiltin="1"/>
+    <cellStyle name="계산" xfId="11" builtinId="22" customBuiltin="1"/>
+    <cellStyle name="나쁨" xfId="7" builtinId="27" customBuiltin="1"/>
+    <cellStyle name="메모" xfId="15" builtinId="10" customBuiltin="1"/>
+    <cellStyle name="백분율" xfId="62" builtinId="5"/>
+    <cellStyle name="보통" xfId="8" builtinId="28" customBuiltin="1"/>
+    <cellStyle name="설명 텍스트" xfId="16" builtinId="53" customBuiltin="1"/>
+    <cellStyle name="셀 확인" xfId="13" builtinId="23" customBuiltin="1"/>
+    <cellStyle name="쉼표" xfId="61" builtinId="3"/>
+    <cellStyle name="연결된 셀" xfId="12" builtinId="24" customBuiltin="1"/>
+    <cellStyle name="열어 본 하이퍼링크" xfId="53" builtinId="9" customBuiltin="1"/>
+    <cellStyle name="요약" xfId="17" builtinId="25" customBuiltin="1"/>
+    <cellStyle name="입력" xfId="9" builtinId="20" customBuiltin="1"/>
+    <cellStyle name="제목" xfId="1" builtinId="15" customBuiltin="1"/>
+    <cellStyle name="제목 1" xfId="2" builtinId="16" customBuiltin="1"/>
+    <cellStyle name="제목 2" xfId="3" builtinId="17" customBuiltin="1"/>
+    <cellStyle name="제목 3" xfId="4" builtinId="18" customBuiltin="1"/>
+    <cellStyle name="제목 4" xfId="5" builtinId="19" customBuiltin="1"/>
+    <cellStyle name="좋음" xfId="6" builtinId="26" customBuiltin="1"/>
+    <cellStyle name="출력" xfId="10" builtinId="21" customBuiltin="1"/>
+    <cellStyle name="표준" xfId="0" builtinId="0"/>
+    <cellStyle name="하이퍼링크" xfId="47" builtinId="8" customBuiltin="1"/>
   </cellStyles>
   <dxfs count="2">
     <dxf>
@@ -4279,42 +4286,42 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C81"/>
-  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
+  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="37.40625" customWidth="1"/>
-    <col min="2" max="2" width="30.54296875" customWidth="1"/>
-    <col min="3" max="3" width="39.40625" customWidth="1"/>
+    <col min="1" max="1" width="37.4140625" customWidth="1"/>
+    <col min="2" max="2" width="30.5" customWidth="1"/>
+    <col min="3" max="3" width="39.4140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.75">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>321</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.75">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A2" s="1" t="s">
         <v>322</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.75">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A3" s="1" t="s">
         <v>315</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.75">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A4" s="1" t="s">
         <v>365</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.75">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A5" s="1" t="s">
         <v>424</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.75">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A6" s="1"/>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.75">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
         <v>45</v>
       </c>
@@ -4323,177 +4330,177 @@
       </c>
       <c r="C7" s="177"/>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.75">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.45">
       <c r="B8" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.75">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.45">
       <c r="B9" s="2">
         <v>2019</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.75">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.45">
       <c r="B10" t="s">
         <v>385</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.75">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.45">
       <c r="B11" s="3" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.75">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.45">
       <c r="B12" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.75">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.45">
       <c r="B14" s="173" t="s">
         <v>401</v>
       </c>
       <c r="C14" s="177"/>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.75">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.45">
       <c r="B15" t="s">
         <v>304</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.75">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.45">
       <c r="B16" s="2">
         <v>2019</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B17" t="s">
         <v>419</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B18" t="s">
         <v>306</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B19" t="s">
         <v>305</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B21" s="173" t="s">
         <v>425</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B22" t="s">
         <v>426</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B23" s="2">
         <v>2021</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B24" t="s">
         <v>427</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B25" t="s">
         <v>428</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B26" t="s">
         <v>429</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A29" s="1" t="s">
         <v>307</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A30" t="s">
         <v>308</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A31" t="s">
         <v>309</v>
       </c>
     </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="33" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A33" t="s">
         <v>394</v>
       </c>
     </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="34" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A34" t="s">
         <v>395</v>
       </c>
     </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="35" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A35" t="s">
         <v>396</v>
       </c>
     </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="36" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A36" t="s">
         <v>397</v>
       </c>
     </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="37" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A37" t="s">
         <v>399</v>
       </c>
     </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="38" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A38" t="s">
         <v>398</v>
       </c>
     </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="40" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A40" t="s">
         <v>361</v>
       </c>
     </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="41" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A41" t="s">
         <v>362</v>
       </c>
     </row>
-    <row r="42" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="42" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A42" t="s">
         <v>363</v>
       </c>
     </row>
-    <row r="44" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="44" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A44" t="s">
         <v>420</v>
       </c>
     </row>
-    <row r="45" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="45" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A45" t="s">
         <v>421</v>
       </c>
     </row>
-    <row r="47" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="47" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A47" s="1" t="s">
         <v>317</v>
       </c>
     </row>
-    <row r="48" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="48" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A48" s="1"/>
     </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.75">
+    <row r="49" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A49" s="174" t="s">
         <v>331</v>
       </c>
       <c r="B49" s="175"/>
     </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.75">
+    <row r="50" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A50" t="s">
         <v>349</v>
       </c>
@@ -4504,7 +4511,7 @@
         <v>359</v>
       </c>
     </row>
-    <row r="51" spans="1:3" ht="29.5" x14ac:dyDescent="0.75">
+    <row r="51" spans="1:3" ht="34" x14ac:dyDescent="0.45">
       <c r="A51" s="176" t="s">
         <v>392</v>
       </c>
@@ -4512,7 +4519,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.75">
+    <row r="52" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A52" t="s">
         <v>324</v>
       </c>
@@ -4520,7 +4527,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.75">
+    <row r="53" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A53" t="s">
         <v>366</v>
       </c>
@@ -4528,7 +4535,7 @@
         <v>393</v>
       </c>
     </row>
-    <row r="54" spans="1:3" ht="44.25" x14ac:dyDescent="0.75">
+    <row r="54" spans="1:3" ht="51" x14ac:dyDescent="0.45">
       <c r="A54" s="176" t="s">
         <v>387</v>
       </c>
@@ -4536,7 +4543,7 @@
         <v>422</v>
       </c>
     </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.75">
+    <row r="55" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A55" s="176" t="s">
         <v>389</v>
       </c>
@@ -4544,7 +4551,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.75">
+    <row r="56" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A56" s="176" t="s">
         <v>356</v>
       </c>
@@ -4555,16 +4562,16 @@
         <v>360</v>
       </c>
     </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.75">
+    <row r="57" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A57" s="176"/>
     </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.75">
+    <row r="58" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A58" s="174" t="s">
         <v>336</v>
       </c>
       <c r="B58" s="175"/>
     </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.75">
+    <row r="59" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A59" t="s">
         <v>349</v>
       </c>
@@ -4572,7 +4579,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="60" spans="1:3" ht="29.5" x14ac:dyDescent="0.75">
+    <row r="60" spans="1:3" ht="34" x14ac:dyDescent="0.45">
       <c r="A60" s="176" t="s">
         <v>392</v>
       </c>
@@ -4580,7 +4587,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.75">
+    <row r="61" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A61" t="s">
         <v>324</v>
       </c>
@@ -4588,7 +4595,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.75">
+    <row r="62" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A62" t="s">
         <v>366</v>
       </c>
@@ -4596,7 +4603,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="63" spans="1:3" ht="44.25" x14ac:dyDescent="0.75">
+    <row r="63" spans="1:3" ht="51" x14ac:dyDescent="0.45">
       <c r="A63" s="176" t="s">
         <v>391</v>
       </c>
@@ -4604,7 +4611,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.75">
+    <row r="64" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A64" s="176" t="s">
         <v>388</v>
       </c>
@@ -4612,7 +4619,7 @@
         <v>423</v>
       </c>
     </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="65" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A65" s="176" t="s">
         <v>354</v>
       </c>
@@ -4620,33 +4627,33 @@
         <v>355</v>
       </c>
     </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="67" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A67" s="174" t="s">
         <v>334</v>
       </c>
     </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="68" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A68" t="s">
         <v>335</v>
       </c>
     </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="70" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A70" s="174" t="s">
         <v>364</v>
       </c>
     </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="71" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A71" t="s">
         <v>357</v>
       </c>
     </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="74" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A74" s="173" t="s">
         <v>316</v>
       </c>
       <c r="B74" s="177"/>
     </row>
-    <row r="75" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="75" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A75">
         <v>42</v>
       </c>
@@ -4654,7 +4661,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="76" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="76" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A76">
         <f>3.41214*10^6</f>
         <v>3412140</v>
@@ -4663,7 +4670,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="77" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="77" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A77">
         <v>61013</v>
       </c>
@@ -4671,13 +4678,14 @@
         <v>431</v>
       </c>
     </row>
-    <row r="79" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="79" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A79" s="1"/>
     </row>
-    <row r="81" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="81" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A81" s="182"/>
     </row>
   </sheetData>
+  <phoneticPr fontId="40" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
 </worksheet>
@@ -4686,14 +4694,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:AK85"/>
-  <sheetFormatPr defaultColWidth="9.1328125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.65"/>
+  <sheetFormatPr defaultColWidth="9.1640625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="20.86328125" style="5" hidden="1" customWidth="1"/>
-    <col min="2" max="2" width="45.7265625" style="5" customWidth="1"/>
-    <col min="3" max="16384" width="9.1328125" style="5"/>
+    <col min="1" max="1" width="20.83203125" style="5" hidden="1" customWidth="1"/>
+    <col min="2" max="2" width="45.75" style="5" customWidth="1"/>
+    <col min="3" max="16384" width="9.1640625" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:37" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.8">
+    <row r="1" spans="1:37" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B1" s="16" t="s">
         <v>386</v>
       </c>
@@ -4800,8 +4808,8 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:37" ht="15" customHeight="1" thickTop="1" x14ac:dyDescent="0.65"/>
-    <row r="3" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.65">
+    <row r="2" spans="1:37" ht="15" customHeight="1" thickTop="1" x14ac:dyDescent="0.3"/>
+    <row r="3" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C3" s="18" t="s">
         <v>121</v>
       </c>
@@ -4812,7 +4820,7 @@
       <c r="F3" s="18"/>
       <c r="G3" s="18"/>
     </row>
-    <row r="4" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.65">
+    <row r="4" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C4" s="18" t="s">
         <v>120</v>
       </c>
@@ -4825,7 +4833,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="5" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.65">
+    <row r="5" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C5" s="18" t="s">
         <v>118</v>
       </c>
@@ -4836,7 +4844,7 @@
       <c r="F5" s="18"/>
       <c r="G5" s="18"/>
     </row>
-    <row r="6" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.65">
+    <row r="6" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C6" s="18" t="s">
         <v>117</v>
       </c>
@@ -4847,7 +4855,7 @@
       <c r="F6" s="18"/>
       <c r="G6" s="18"/>
     </row>
-    <row r="10" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.8">
+    <row r="10" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="7" t="s">
         <v>116</v>
       </c>
@@ -4855,12 +4863,12 @@
         <v>115</v>
       </c>
     </row>
-    <row r="11" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.65">
+    <row r="11" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B11" s="16" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.65">
+    <row r="12" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B12" s="16" t="s">
         <v>2</v>
       </c>
@@ -4970,7 +4978,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="13" spans="1:37" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.8">
+    <row r="13" spans="1:37" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B13" s="14" t="s">
         <v>2</v>
       </c>
@@ -5080,17 +5088,17 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="14" spans="1:37" ht="15" customHeight="1" thickTop="1" x14ac:dyDescent="0.65">
+    <row r="14" spans="1:37" ht="15" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
       <c r="B14" s="11" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="15" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.65">
+    <row r="15" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B15" s="11" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="16" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.75">
+    <row r="16" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A16" s="7" t="s">
         <v>114</v>
       </c>
@@ -5203,7 +5211,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.75">
+    <row r="17" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A17" s="7" t="s">
         <v>113</v>
       </c>
@@ -5316,7 +5324,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.75">
+    <row r="18" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A18" s="7" t="s">
         <v>112</v>
       </c>
@@ -5429,7 +5437,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.75">
+    <row r="19" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A19" s="7" t="s">
         <v>111</v>
       </c>
@@ -5542,7 +5550,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.75">
+    <row r="20" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A20" s="7" t="s">
         <v>110</v>
       </c>
@@ -5655,7 +5663,7 @@
         <v>-1.1E-5</v>
       </c>
     </row>
-    <row r="21" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.75">
+    <row r="21" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A21" s="7" t="s">
         <v>109</v>
       </c>
@@ -5768,7 +5776,7 @@
         <v>-1.1E-5</v>
       </c>
     </row>
-    <row r="22" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.75">
+    <row r="22" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A22" s="7" t="s">
         <v>108</v>
       </c>
@@ -5881,7 +5889,7 @@
         <v>-1.1E-5</v>
       </c>
     </row>
-    <row r="23" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.75">
+    <row r="23" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A23" s="7" t="s">
         <v>107</v>
       </c>
@@ -5994,7 +6002,7 @@
         <v>-1.1E-5</v>
       </c>
     </row>
-    <row r="24" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.75">
+    <row r="24" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A24" s="7" t="s">
         <v>106</v>
       </c>
@@ -6107,7 +6115,7 @@
         <v>-1.1E-5</v>
       </c>
     </row>
-    <row r="25" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.75">
+    <row r="25" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A25" s="7" t="s">
         <v>105</v>
       </c>
@@ -6220,7 +6228,7 @@
         <v>-1.1E-5</v>
       </c>
     </row>
-    <row r="26" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.75">
+    <row r="26" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A26" s="7" t="s">
         <v>104</v>
       </c>
@@ -6333,7 +6341,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.75">
+    <row r="27" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A27" s="7" t="s">
         <v>103</v>
       </c>
@@ -6446,7 +6454,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.75">
+    <row r="28" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A28" s="7" t="s">
         <v>102</v>
       </c>
@@ -6559,7 +6567,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.75">
+    <row r="29" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A29" s="7" t="s">
         <v>100</v>
       </c>
@@ -6672,7 +6680,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.75">
+    <row r="30" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A30" s="7" t="s">
         <v>99</v>
       </c>
@@ -6785,7 +6793,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.75">
+    <row r="31" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A31" s="7" t="s">
         <v>98</v>
       </c>
@@ -6898,7 +6906,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.75">
+    <row r="32" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A32" s="7" t="s">
         <v>97</v>
       </c>
@@ -7011,7 +7019,7 @@
         <v>-2.0000000000000001E-4</v>
       </c>
     </row>
-    <row r="33" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.75">
+    <row r="33" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A33" s="7" t="s">
         <v>96</v>
       </c>
@@ -7124,7 +7132,7 @@
         <v>-2.1599999999999999E-4</v>
       </c>
     </row>
-    <row r="34" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.75">
+    <row r="34" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A34" s="7" t="s">
         <v>95</v>
       </c>
@@ -7237,7 +7245,7 @@
         <v>-2.2499999999999999E-4</v>
       </c>
     </row>
-    <row r="35" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.75">
+    <row r="35" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A35" s="7" t="s">
         <v>379</v>
       </c>
@@ -7350,7 +7358,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.75">
+    <row r="36" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A36" s="7" t="s">
         <v>377</v>
       </c>
@@ -7463,7 +7471,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.75">
+    <row r="37" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A37" s="7" t="s">
         <v>94</v>
       </c>
@@ -7576,7 +7584,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.75">
+    <row r="38" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A38" s="7" t="s">
         <v>93</v>
       </c>
@@ -7689,7 +7697,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.75">
+    <row r="39" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A39" s="7" t="s">
         <v>92</v>
       </c>
@@ -7802,7 +7810,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.75">
+    <row r="40" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A40" s="7" t="s">
         <v>91</v>
       </c>
@@ -7915,7 +7923,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.75">
+    <row r="41" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A41" s="7" t="s">
         <v>90</v>
       </c>
@@ -8028,7 +8036,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.75">
+    <row r="42" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A42" s="7" t="s">
         <v>89</v>
       </c>
@@ -8141,7 +8149,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.75">
+    <row r="43" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A43" s="7" t="s">
         <v>88</v>
       </c>
@@ -8254,7 +8262,7 @@
         <v>1.9699999999999999E-4</v>
       </c>
     </row>
-    <row r="44" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.75">
+    <row r="44" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A44" s="7" t="s">
         <v>87</v>
       </c>
@@ -8367,7 +8375,7 @@
         <v>-4.8299999999999998E-4</v>
       </c>
     </row>
-    <row r="45" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.75">
+    <row r="45" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A45" s="7" t="s">
         <v>86</v>
       </c>
@@ -8480,7 +8488,7 @@
         <v>-3.1150000000000001E-3</v>
       </c>
     </row>
-    <row r="46" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.75">
+    <row r="46" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A46" s="7" t="s">
         <v>85</v>
       </c>
@@ -8593,12 +8601,12 @@
         <v>-1.013E-3</v>
       </c>
     </row>
-    <row r="47" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.65">
+    <row r="47" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B47" s="13" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="48" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.75">
+    <row r="48" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A48" s="7" t="s">
         <v>84</v>
       </c>
@@ -8711,7 +8719,7 @@
         <v>-2.4000000000000001E-4</v>
       </c>
     </row>
-    <row r="49" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.75">
+    <row r="49" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A49" s="7" t="s">
         <v>83</v>
       </c>
@@ -8824,7 +8832,7 @@
         <v>-3.0000000000000001E-6</v>
       </c>
     </row>
-    <row r="50" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.75">
+    <row r="50" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A50" s="7" t="s">
         <v>82</v>
       </c>
@@ -8937,7 +8945,7 @@
         <v>2.3E-5</v>
       </c>
     </row>
-    <row r="51" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.75">
+    <row r="51" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A51" s="7" t="s">
         <v>81</v>
       </c>
@@ -9050,12 +9058,12 @@
         <v>-2.7700000000000001E-4</v>
       </c>
     </row>
-    <row r="53" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.65">
+    <row r="53" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B53" s="11" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="54" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.75">
+    <row r="54" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A54" s="7" t="s">
         <v>80</v>
       </c>
@@ -9168,7 +9176,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.75">
+    <row r="55" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A55" s="7" t="s">
         <v>79</v>
       </c>
@@ -9281,7 +9289,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.75">
+    <row r="56" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A56" s="7" t="s">
         <v>78</v>
       </c>
@@ -9394,7 +9402,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.75">
+    <row r="57" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A57" s="7" t="s">
         <v>77</v>
       </c>
@@ -9507,7 +9515,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.75">
+    <row r="58" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A58" s="7" t="s">
         <v>76</v>
       </c>
@@ -9620,7 +9628,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.75">
+    <row r="59" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A59" s="7" t="s">
         <v>75</v>
       </c>
@@ -9733,7 +9741,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.75">
+    <row r="60" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A60" s="7" t="s">
         <v>74</v>
       </c>
@@ -9846,12 +9854,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.65">
+    <row r="62" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B62" s="11" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="63" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.75">
+    <row r="63" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A63" s="7" t="s">
         <v>73</v>
       </c>
@@ -9964,7 +9972,7 @@
         <v>-1.4100000000000001E-4</v>
       </c>
     </row>
-    <row r="64" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.75">
+    <row r="64" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A64" s="7" t="s">
         <v>72</v>
       </c>
@@ -10077,7 +10085,7 @@
         <v>-1.0139999999999999E-3</v>
       </c>
     </row>
-    <row r="65" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.75">
+    <row r="65" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A65" s="7" t="s">
         <v>71</v>
       </c>
@@ -10190,7 +10198,7 @@
         <v>-2.1699999999999999E-4</v>
       </c>
     </row>
-    <row r="66" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.75">
+    <row r="66" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A66" s="7" t="s">
         <v>70</v>
       </c>
@@ -10303,7 +10311,7 @@
         <v>2.8499999999999999E-4</v>
       </c>
     </row>
-    <row r="67" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.75">
+    <row r="67" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A67" s="7" t="s">
         <v>69</v>
       </c>
@@ -10416,7 +10424,7 @@
         <v>2.3E-5</v>
       </c>
     </row>
-    <row r="68" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.75">
+    <row r="68" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A68" s="7" t="s">
         <v>68</v>
       </c>
@@ -10529,7 +10537,7 @@
         <v>-5.5000000000000002E-5</v>
       </c>
     </row>
-    <row r="69" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.75">
+    <row r="69" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A69" s="7" t="s">
         <v>67</v>
       </c>
@@ -10642,7 +10650,7 @@
         <v>-9.5000000000000005E-5</v>
       </c>
     </row>
-    <row r="70" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.75">
+    <row r="70" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A70" s="7" t="s">
         <v>66</v>
       </c>
@@ -10755,7 +10763,7 @@
         <v>2.5799999999999998E-4</v>
       </c>
     </row>
-    <row r="71" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.75">
+    <row r="71" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A71" s="7" t="s">
         <v>65</v>
       </c>
@@ -10868,7 +10876,7 @@
         <v>5.7700000000000004E-4</v>
       </c>
     </row>
-    <row r="72" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.75">
+    <row r="72" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A72" s="7" t="s">
         <v>64</v>
       </c>
@@ -10981,7 +10989,7 @@
         <v>-1.2830000000000001E-3</v>
       </c>
     </row>
-    <row r="73" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.75">
+    <row r="73" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A73" s="7" t="s">
         <v>63</v>
       </c>
@@ -11094,7 +11102,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="74" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.75">
+    <row r="74" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A74" s="7" t="s">
         <v>62</v>
       </c>
@@ -11207,7 +11215,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.65">
+    <row r="76" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A76" s="7" t="s">
         <v>61</v>
       </c>
@@ -11320,8 +11328,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:37" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.8"/>
-    <row r="78" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.65">
+    <row r="77" spans="1:37" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="78" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B78" s="183" t="s">
         <v>57</v>
       </c>
@@ -11361,37 +11369,37 @@
       <c r="AJ78" s="183"/>
       <c r="AK78" s="183"/>
     </row>
-    <row r="79" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.65">
+    <row r="79" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B79" s="6" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="80" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.65">
+    <row r="80" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B80" s="6" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="81" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.65">
+    <row r="81" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B81" s="6" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="82" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.65">
+    <row r="82" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B82" s="6" t="s">
         <v>375</v>
       </c>
     </row>
-    <row r="83" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.65">
+    <row r="83" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B83" s="6" t="s">
         <v>374</v>
       </c>
     </row>
-    <row r="84" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.65">
+    <row r="84" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B84" s="6" t="s">
         <v>373</v>
       </c>
     </row>
-    <row r="85" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.65">
+    <row r="85" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B85" s="6" t="s">
         <v>372</v>
       </c>
@@ -11400,6 +11408,7 @@
   <mergeCells count="1">
     <mergeCell ref="B78:AK78"/>
   </mergeCells>
+  <phoneticPr fontId="40" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
@@ -11408,35 +11417,35 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:X163"/>
-  <sheetFormatPr defaultColWidth="9.1328125" defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
+  <sheetFormatPr defaultColWidth="9.1640625" defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="33.1328125" customWidth="1"/>
-    <col min="2" max="2" width="13.40625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.54296875" customWidth="1"/>
-    <col min="4" max="4" width="12.86328125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.40625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.26953125" customWidth="1"/>
-    <col min="7" max="7" width="13.40625" customWidth="1"/>
-    <col min="8" max="8" width="12.7265625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="9.7265625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="10.40625" customWidth="1"/>
-    <col min="12" max="12" width="12.40625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="12.86328125" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="10.40625" customWidth="1"/>
-    <col min="23" max="23" width="10.7265625" customWidth="1"/>
+    <col min="1" max="1" width="33.1640625" customWidth="1"/>
+    <col min="2" max="2" width="13.4140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.5" customWidth="1"/>
+    <col min="4" max="4" width="12.83203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.4140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.25" customWidth="1"/>
+    <col min="7" max="7" width="13.4140625" customWidth="1"/>
+    <col min="8" max="8" width="12.75" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="9.75" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="10.4140625" customWidth="1"/>
+    <col min="12" max="12" width="12.4140625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="12.83203125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="10.4140625" customWidth="1"/>
+    <col min="23" max="23" width="10.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23" ht="15.75" x14ac:dyDescent="0.75">
+    <row r="1" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A1" s="19" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="2" spans="1:23" x14ac:dyDescent="0.75">
+    <row r="2" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A2" s="20" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="3" spans="1:23" ht="12.75" customHeight="1" x14ac:dyDescent="0.75">
+    <row r="3" spans="1:23" ht="12.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A3" s="21" t="s">
         <v>126</v>
       </c>
@@ -11459,7 +11468,7 @@
       </c>
       <c r="I3" s="25"/>
     </row>
-    <row r="4" spans="1:23" ht="26.75" x14ac:dyDescent="0.75">
+    <row r="4" spans="1:23" ht="27.5" x14ac:dyDescent="0.45">
       <c r="A4" s="26"/>
       <c r="B4" s="27" t="s">
         <v>302</v>
@@ -11484,7 +11493,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="5" spans="1:23" x14ac:dyDescent="0.75">
+    <row r="5" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A5" s="31" t="s">
         <v>137</v>
       </c>
@@ -11501,7 +11510,7 @@
       <c r="H5" s="34"/>
       <c r="I5" s="35"/>
     </row>
-    <row r="6" spans="1:23" x14ac:dyDescent="0.75">
+    <row r="6" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A6" s="36" t="s">
         <v>139</v>
       </c>
@@ -11522,7 +11531,7 @@
       <c r="H6" s="39"/>
       <c r="I6" s="40"/>
     </row>
-    <row r="7" spans="1:23" x14ac:dyDescent="0.75">
+    <row r="7" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A7" s="41" t="s">
         <v>142</v>
       </c>
@@ -11551,7 +11560,7 @@
         <v>0.93726057101554028</v>
       </c>
     </row>
-    <row r="8" spans="1:23" x14ac:dyDescent="0.75">
+    <row r="8" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A8" s="41" t="s">
         <v>143</v>
       </c>
@@ -11580,7 +11589,7 @@
         <v>0.93500000000000005</v>
       </c>
     </row>
-    <row r="9" spans="1:23" x14ac:dyDescent="0.75">
+    <row r="9" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A9" s="41" t="s">
         <v>144</v>
       </c>
@@ -11609,7 +11618,7 @@
         <v>0.93500000000000016</v>
       </c>
     </row>
-    <row r="10" spans="1:23" x14ac:dyDescent="0.75">
+    <row r="10" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A10" s="41" t="s">
         <v>145</v>
       </c>
@@ -11638,7 +11647,7 @@
         <v>0.93500000000000016</v>
       </c>
     </row>
-    <row r="11" spans="1:23" x14ac:dyDescent="0.75">
+    <row r="11" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A11" s="41" t="s">
         <v>146</v>
       </c>
@@ -11675,7 +11684,7 @@
       <c r="R11" s="46"/>
       <c r="S11" s="52"/>
     </row>
-    <row r="12" spans="1:23" x14ac:dyDescent="0.75">
+    <row r="12" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A12" s="41" t="s">
         <v>147</v>
       </c>
@@ -11704,7 +11713,7 @@
         <v>0.93500000000000005</v>
       </c>
     </row>
-    <row r="13" spans="1:23" x14ac:dyDescent="0.75">
+    <row r="13" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
         <v>148</v>
       </c>
@@ -11733,7 +11742,7 @@
         <v>0.93726057101554028</v>
       </c>
     </row>
-    <row r="14" spans="1:23" x14ac:dyDescent="0.75">
+    <row r="14" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
         <v>149</v>
       </c>
@@ -11762,7 +11771,7 @@
         <v>0.93726057101554017</v>
       </c>
     </row>
-    <row r="15" spans="1:23" x14ac:dyDescent="0.75">
+    <row r="15" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A15" s="41" t="s">
         <v>150</v>
       </c>
@@ -11799,7 +11808,7 @@
       <c r="V15" s="57"/>
       <c r="W15" s="53"/>
     </row>
-    <row r="16" spans="1:23" x14ac:dyDescent="0.75">
+    <row r="16" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A16" s="41" t="s">
         <v>151</v>
       </c>
@@ -11833,7 +11842,7 @@
       <c r="V16" s="57"/>
       <c r="W16" s="53"/>
     </row>
-    <row r="17" spans="1:23" x14ac:dyDescent="0.75">
+    <row r="17" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A17" s="41" t="s">
         <v>152</v>
       </c>
@@ -11870,7 +11879,7 @@
       <c r="V17" s="57"/>
       <c r="W17" s="53"/>
     </row>
-    <row r="18" spans="1:23" x14ac:dyDescent="0.75">
+    <row r="18" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A18" s="41" t="s">
         <v>153</v>
       </c>
@@ -11904,7 +11913,7 @@
       <c r="V18" s="57"/>
       <c r="W18" s="53"/>
     </row>
-    <row r="19" spans="1:23" x14ac:dyDescent="0.75">
+    <row r="19" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A19" s="41" t="s">
         <v>154</v>
       </c>
@@ -11938,7 +11947,7 @@
       <c r="M19" s="57"/>
       <c r="N19" s="53"/>
     </row>
-    <row r="20" spans="1:23" x14ac:dyDescent="0.75">
+    <row r="20" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A20" s="41" t="s">
         <v>303</v>
       </c>
@@ -11968,7 +11977,7 @@
       </c>
       <c r="W20" s="53"/>
     </row>
-    <row r="21" spans="1:23" x14ac:dyDescent="0.75">
+    <row r="21" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A21" s="59" t="s">
         <v>406</v>
       </c>
@@ -11995,7 +12004,7 @@
       </c>
       <c r="I21" s="47"/>
     </row>
-    <row r="22" spans="1:23" x14ac:dyDescent="0.75">
+    <row r="22" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A22" s="41" t="s">
         <v>155</v>
       </c>
@@ -12024,7 +12033,7 @@
         <v>0.93499781627602274</v>
       </c>
     </row>
-    <row r="23" spans="1:23" x14ac:dyDescent="0.75">
+    <row r="23" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A23" s="41" t="s">
         <v>156</v>
       </c>
@@ -12053,7 +12062,7 @@
         <v>0.93499781627602274</v>
       </c>
     </row>
-    <row r="24" spans="1:23" x14ac:dyDescent="0.75">
+    <row r="24" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A24" s="41" t="s">
         <v>157</v>
       </c>
@@ -12082,7 +12091,7 @@
         <v>0.93476175247841387</v>
       </c>
     </row>
-    <row r="25" spans="1:23" x14ac:dyDescent="0.75">
+    <row r="25" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A25" s="41" t="s">
         <v>407</v>
       </c>
@@ -12111,7 +12120,7 @@
         <v>0.93404711473172097</v>
       </c>
     </row>
-    <row r="26" spans="1:23" x14ac:dyDescent="0.75">
+    <row r="26" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A26" s="41" t="s">
         <v>158</v>
       </c>
@@ -12140,7 +12149,7 @@
         <v>0.93500003751584637</v>
       </c>
     </row>
-    <row r="27" spans="1:23" x14ac:dyDescent="0.75">
+    <row r="27" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A27" s="41" t="s">
         <v>159</v>
       </c>
@@ -12169,7 +12178,7 @@
         <v>0.93500003751584626</v>
       </c>
     </row>
-    <row r="28" spans="1:23" x14ac:dyDescent="0.75">
+    <row r="28" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A28" s="41" t="s">
         <v>160</v>
       </c>
@@ -12198,7 +12207,7 @@
         <v>0.93135126106564226</v>
       </c>
     </row>
-    <row r="29" spans="1:23" x14ac:dyDescent="0.75">
+    <row r="29" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A29" s="41" t="s">
         <v>161</v>
       </c>
@@ -12227,7 +12236,7 @@
         <v>0.93499781627602263</v>
       </c>
     </row>
-    <row r="30" spans="1:23" x14ac:dyDescent="0.75">
+    <row r="30" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A30" s="41" t="s">
         <v>162</v>
       </c>
@@ -12256,7 +12265,7 @@
         <v>0.93499781627602263</v>
       </c>
     </row>
-    <row r="31" spans="1:23" x14ac:dyDescent="0.75">
+    <row r="31" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A31" s="41" t="s">
         <v>163</v>
       </c>
@@ -12285,7 +12294,7 @@
         <v>0.87806748466257667</v>
       </c>
     </row>
-    <row r="32" spans="1:23" x14ac:dyDescent="0.75">
+    <row r="32" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A32" s="41" t="s">
         <v>164</v>
       </c>
@@ -12314,7 +12323,7 @@
         <v>0.90299302022950434</v>
       </c>
     </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.75">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A33" s="41" t="s">
         <v>165</v>
       </c>
@@ -12343,7 +12352,7 @@
         <v>0.92051300964428628</v>
       </c>
     </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.75">
+    <row r="34" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A34" s="41" t="s">
         <v>166</v>
       </c>
@@ -12372,7 +12381,7 @@
         <v>0.92867915675168411</v>
       </c>
     </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.75">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A35" s="41" t="s">
         <v>167</v>
       </c>
@@ -12401,7 +12410,7 @@
         <v>0.93364967025896739</v>
       </c>
     </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.75">
+    <row r="36" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A36" s="41" t="s">
         <v>168</v>
       </c>
@@ -12430,7 +12439,7 @@
         <v>0.9293293950333662</v>
       </c>
     </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.75">
+    <row r="37" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A37" s="41" t="s">
         <v>169</v>
       </c>
@@ -12459,7 +12468,7 @@
         <v>0.88092431030417351</v>
       </c>
     </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.75">
+    <row r="38" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A38" s="41" t="s">
         <v>170</v>
       </c>
@@ -12488,7 +12497,7 @@
         <v>0.91165189789710355</v>
       </c>
     </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.75">
+    <row r="39" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A39" s="41" t="s">
         <v>171</v>
       </c>
@@ -12517,7 +12526,7 @@
         <v>0.91165189789710355</v>
       </c>
     </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.75">
+    <row r="40" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A40" s="41" t="s">
         <v>172</v>
       </c>
@@ -12546,7 +12555,7 @@
         <v>0.93427633635511098</v>
       </c>
     </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.75">
+    <row r="41" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A41" s="41" t="s">
         <v>173</v>
       </c>
@@ -12575,7 +12584,7 @@
         <v>0.95108821041298164</v>
       </c>
     </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.75">
+    <row r="42" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A42" s="41" t="s">
         <v>174</v>
       </c>
@@ -12604,7 +12613,7 @@
         <v>0.93427633635511098</v>
       </c>
     </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.75">
+    <row r="43" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A43" s="41" t="s">
         <v>175</v>
       </c>
@@ -12633,7 +12642,7 @@
         <v>0.93938096730547249</v>
       </c>
     </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.75">
+    <row r="44" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A44" s="41" t="s">
         <v>176</v>
       </c>
@@ -12662,7 +12671,7 @@
         <v>0.92840083590406852</v>
       </c>
     </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.75">
+    <row r="45" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A45" t="s">
         <v>177</v>
       </c>
@@ -12691,7 +12700,7 @@
         <v>0.93361506882395562</v>
       </c>
     </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.75">
+    <row r="46" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A46" s="41" t="s">
         <v>178</v>
       </c>
@@ -12720,7 +12729,7 @@
         <v>0.93361506882395551</v>
       </c>
     </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.75">
+    <row r="47" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A47" s="41" t="s">
         <v>408</v>
       </c>
@@ -12749,7 +12758,7 @@
         <v>0.93361506882395551</v>
       </c>
     </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.75">
+    <row r="48" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A48" s="41" t="s">
         <v>179</v>
       </c>
@@ -12778,7 +12787,7 @@
         <v>0.93500003751584626</v>
       </c>
     </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.75">
+    <row r="49" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A49" s="41" t="s">
         <v>180</v>
       </c>
@@ -12807,7 +12816,7 @@
         <v>0.84675180455302612</v>
       </c>
     </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.75">
+    <row r="50" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A50" s="41" t="s">
         <v>181</v>
       </c>
@@ -12836,7 +12845,7 @@
         <v>0.92494808662118067</v>
       </c>
     </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.75">
+    <row r="51" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A51" s="41" t="s">
         <v>182</v>
       </c>
@@ -12865,7 +12874,7 @@
         <v>0.92528460728977324</v>
       </c>
     </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.75">
+    <row r="52" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A52" s="41" t="s">
         <v>183</v>
       </c>
@@ -12894,7 +12903,7 @@
         <v>0.92548586165607438</v>
       </c>
     </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.75">
+    <row r="53" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A53" s="41" t="s">
         <v>184</v>
       </c>
@@ -12923,7 +12932,7 @@
         <v>0.92007362914163926</v>
       </c>
     </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.75">
+    <row r="54" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A54" s="41" t="s">
         <v>185</v>
       </c>
@@ -12952,7 +12961,7 @@
         <v>0.91375811688311692</v>
       </c>
     </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.75">
+    <row r="55" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A55" s="41" t="s">
         <v>186</v>
       </c>
@@ -12981,7 +12990,7 @@
         <v>0.92923017182797785</v>
       </c>
     </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.75">
+    <row r="56" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A56" s="41" t="s">
         <v>187</v>
       </c>
@@ -13010,7 +13019,7 @@
         <v>0.92157077225989936</v>
       </c>
     </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.75">
+    <row r="57" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A57" s="41" t="s">
         <v>188</v>
       </c>
@@ -13037,7 +13046,7 @@
         <v>0.92932939503336609</v>
       </c>
     </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.75">
+    <row r="58" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A58" s="36" t="s">
         <v>189</v>
       </c>
@@ -13066,7 +13075,7 @@
         <v>0.93722267739953979</v>
       </c>
     </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.75">
+    <row r="59" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A59" s="41" t="s">
         <v>191</v>
       </c>
@@ -13089,7 +13098,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.75">
+    <row r="60" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A60" s="41" t="s">
         <v>194</v>
       </c>
@@ -13118,7 +13127,7 @@
         <v>0.90266299357208446</v>
       </c>
     </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.75">
+    <row r="61" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A61" s="41" t="s">
         <v>195</v>
       </c>
@@ -13147,7 +13156,7 @@
         <v>0.9009009009009008</v>
       </c>
     </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.75">
+    <row r="62" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A62" s="41" t="s">
         <v>196</v>
       </c>
@@ -13176,7 +13185,7 @@
         <v>0.84548104956268222</v>
       </c>
     </row>
-    <row r="63" spans="1:9" x14ac:dyDescent="0.75">
+    <row r="63" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A63" s="41" t="s">
         <v>197</v>
       </c>
@@ -13197,7 +13206,7 @@
       </c>
       <c r="I63" s="47"/>
     </row>
-    <row r="64" spans="1:9" x14ac:dyDescent="0.75">
+    <row r="64" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A64" s="36" t="s">
         <v>190</v>
       </c>
@@ -13226,7 +13235,7 @@
         <v>0.90586790472651468</v>
       </c>
     </row>
-    <row r="65" spans="1:12" x14ac:dyDescent="0.75">
+    <row r="65" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A65" s="41" t="s">
         <v>198</v>
       </c>
@@ -13247,7 +13256,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="66" spans="1:12" x14ac:dyDescent="0.75">
+    <row r="66" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A66" s="59" t="s">
         <v>200</v>
       </c>
@@ -13273,7 +13282,7 @@
       <c r="I66" s="81"/>
       <c r="K66" s="82"/>
     </row>
-    <row r="67" spans="1:12" x14ac:dyDescent="0.75">
+    <row r="67" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A67" s="59" t="s">
         <v>201</v>
       </c>
@@ -13301,7 +13310,7 @@
       </c>
       <c r="K67" s="82"/>
     </row>
-    <row r="68" spans="1:12" x14ac:dyDescent="0.75">
+    <row r="68" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A68" s="59" t="s">
         <v>202</v>
       </c>
@@ -13329,7 +13338,7 @@
       </c>
       <c r="K68" s="82"/>
     </row>
-    <row r="69" spans="1:12" x14ac:dyDescent="0.75">
+    <row r="69" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A69" s="59" t="s">
         <v>203</v>
       </c>
@@ -13357,7 +13366,7 @@
       </c>
       <c r="K69" s="82"/>
     </row>
-    <row r="70" spans="1:12" x14ac:dyDescent="0.75">
+    <row r="70" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A70" s="59" t="s">
         <v>204</v>
       </c>
@@ -13385,7 +13394,7 @@
       </c>
       <c r="K70" s="82"/>
     </row>
-    <row r="71" spans="1:12" x14ac:dyDescent="0.75">
+    <row r="71" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A71" s="41" t="s">
         <v>205</v>
       </c>
@@ -13414,7 +13423,7 @@
       <c r="K71" s="82"/>
       <c r="L71" s="82"/>
     </row>
-    <row r="72" spans="1:12" x14ac:dyDescent="0.75">
+    <row r="72" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A72" s="41" t="s">
         <v>206</v>
       </c>
@@ -13442,7 +13451,7 @@
       </c>
       <c r="K72" s="82"/>
     </row>
-    <row r="73" spans="1:12" x14ac:dyDescent="0.75">
+    <row r="73" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A73" s="41" t="s">
         <v>207</v>
       </c>
@@ -13469,7 +13478,7 @@
         <v>0.94242199100000001</v>
       </c>
     </row>
-    <row r="74" spans="1:12" ht="12.65" customHeight="1" x14ac:dyDescent="0.75">
+    <row r="74" spans="1:12" ht="12.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A74" s="41" t="s">
         <v>208</v>
       </c>
@@ -13497,7 +13506,7 @@
       </c>
       <c r="K74" s="84"/>
     </row>
-    <row r="75" spans="1:12" x14ac:dyDescent="0.75">
+    <row r="75" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A75" s="41" t="s">
         <v>409</v>
       </c>
@@ -13525,7 +13534,7 @@
       </c>
       <c r="K75" s="84"/>
     </row>
-    <row r="76" spans="1:12" x14ac:dyDescent="0.75">
+    <row r="76" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A76" s="41" t="s">
         <v>209</v>
       </c>
@@ -13552,7 +13561,7 @@
         <v>0.93173565722585328</v>
       </c>
     </row>
-    <row r="77" spans="1:12" x14ac:dyDescent="0.75">
+    <row r="77" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A77" s="41" t="s">
         <v>210</v>
       </c>
@@ -13580,7 +13589,7 @@
       </c>
       <c r="K77" s="85"/>
     </row>
-    <row r="78" spans="1:12" x14ac:dyDescent="0.75">
+    <row r="78" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A78" s="41" t="s">
         <v>211</v>
       </c>
@@ -13608,7 +13617,7 @@
       </c>
       <c r="K78" s="84"/>
     </row>
-    <row r="79" spans="1:12" x14ac:dyDescent="0.75">
+    <row r="79" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A79" s="41" t="s">
         <v>212</v>
       </c>
@@ -13635,7 +13644,7 @@
         <v>0.93680161201685286</v>
       </c>
     </row>
-    <row r="80" spans="1:12" x14ac:dyDescent="0.75">
+    <row r="80" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A80" s="41" t="s">
         <v>213</v>
       </c>
@@ -13662,7 +13671,7 @@
         <v>0.93292760238366934</v>
       </c>
     </row>
-    <row r="81" spans="1:14" x14ac:dyDescent="0.75">
+    <row r="81" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A81" s="41" t="s">
         <v>214</v>
       </c>
@@ -13689,7 +13698,7 @@
         <v>0.96554227633195577</v>
       </c>
     </row>
-    <row r="82" spans="1:14" x14ac:dyDescent="0.75">
+    <row r="82" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A82" s="41" t="s">
         <v>410</v>
       </c>
@@ -13716,7 +13725,7 @@
         <v>0.93359512366662756</v>
       </c>
     </row>
-    <row r="83" spans="1:14" x14ac:dyDescent="0.75">
+    <row r="83" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A83" s="59" t="s">
         <v>215</v>
       </c>
@@ -13739,7 +13748,7 @@
       </c>
       <c r="I83" s="88"/>
     </row>
-    <row r="84" spans="1:14" x14ac:dyDescent="0.75">
+    <row r="84" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A84" s="89" t="s">
         <v>216</v>
       </c>
@@ -13762,7 +13771,7 @@
         <v>0.85292563033160751</v>
       </c>
     </row>
-    <row r="85" spans="1:14" x14ac:dyDescent="0.75">
+    <row r="85" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A85" s="89" t="s">
         <v>217</v>
       </c>
@@ -13785,7 +13794,7 @@
         <v>0.88047037071579148</v>
       </c>
     </row>
-    <row r="86" spans="1:14" x14ac:dyDescent="0.75">
+    <row r="86" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A86" s="89" t="s">
         <v>218</v>
       </c>
@@ -13812,7 +13821,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="87" spans="1:14" x14ac:dyDescent="0.75">
+    <row r="87" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A87" s="92" t="s">
         <v>219</v>
       </c>
@@ -13839,7 +13848,7 @@
         <v>0.90447216306662592</v>
       </c>
     </row>
-    <row r="88" spans="1:14" x14ac:dyDescent="0.75">
+    <row r="88" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A88" s="93" t="s">
         <v>220</v>
       </c>
@@ -13866,7 +13875,7 @@
         <v>0.94150280898876404</v>
       </c>
     </row>
-    <row r="89" spans="1:14" x14ac:dyDescent="0.75">
+    <row r="89" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A89" t="s">
         <v>221</v>
       </c>
@@ -13893,7 +13902,7 @@
         <v>0.94150280898876404</v>
       </c>
     </row>
-    <row r="90" spans="1:14" x14ac:dyDescent="0.75">
+    <row r="90" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A90" s="20" t="s">
         <v>222</v>
       </c>
@@ -13920,7 +13929,7 @@
         <v>0.8252427184466018</v>
       </c>
     </row>
-    <row r="91" spans="1:14" x14ac:dyDescent="0.75">
+    <row r="91" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A91" t="s">
         <v>223</v>
       </c>
@@ -13947,7 +13956,7 @@
         <v>0.87681159420289856</v>
       </c>
     </row>
-    <row r="92" spans="1:14" x14ac:dyDescent="0.75">
+    <row r="92" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A92" s="104" t="s">
         <v>411</v>
       </c>
@@ -13981,7 +13990,7 @@
       <c r="M92" s="107"/>
       <c r="N92" s="108"/>
     </row>
-    <row r="93" spans="1:14" x14ac:dyDescent="0.75">
+    <row r="93" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A93" s="109" t="s">
         <v>412</v>
       </c>
@@ -14007,19 +14016,19 @@
       <c r="M93" s="111"/>
       <c r="N93" s="112"/>
     </row>
-    <row r="94" spans="1:14" x14ac:dyDescent="0.75">
+    <row r="94" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A94" s="113"/>
       <c r="B94" s="114"/>
       <c r="N94" s="115"/>
     </row>
-    <row r="95" spans="1:14" x14ac:dyDescent="0.75">
+    <row r="95" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A95" s="113" t="s">
         <v>224</v>
       </c>
       <c r="B95" s="114"/>
       <c r="N95" s="115"/>
     </row>
-    <row r="96" spans="1:14" x14ac:dyDescent="0.75">
+    <row r="96" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A96" s="109" t="s">
         <v>225</v>
       </c>
@@ -14037,7 +14046,7 @@
       <c r="M96" s="117"/>
       <c r="N96" s="118"/>
     </row>
-    <row r="97" spans="1:14" x14ac:dyDescent="0.75">
+    <row r="97" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A97" s="119" t="s">
         <v>226</v>
       </c>
@@ -14081,7 +14090,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="98" spans="1:14" x14ac:dyDescent="0.75">
+    <row r="98" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A98" s="2" t="s">
         <v>233</v>
       </c>
@@ -14125,7 +14134,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="99" spans="1:14" x14ac:dyDescent="0.75">
+    <row r="99" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A99" s="120" t="s">
         <v>234</v>
       </c>
@@ -14169,7 +14178,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="100" spans="1:14" x14ac:dyDescent="0.75">
+    <row r="100" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A100" s="109" t="s">
         <v>235</v>
       </c>
@@ -14213,7 +14222,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="101" spans="1:14" x14ac:dyDescent="0.75">
+    <row r="101" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A101" s="113" t="s">
         <v>236</v>
       </c>
@@ -14257,19 +14266,19 @@
         <v>270</v>
       </c>
     </row>
-    <row r="102" spans="1:14" x14ac:dyDescent="0.75">
+    <row r="102" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A102" s="113"/>
       <c r="B102" s="114"/>
       <c r="G102" s="115"/>
     </row>
-    <row r="103" spans="1:14" x14ac:dyDescent="0.75">
+    <row r="103" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A103" s="113" t="s">
         <v>237</v>
       </c>
       <c r="B103" s="114"/>
       <c r="G103" s="115"/>
     </row>
-    <row r="104" spans="1:14" x14ac:dyDescent="0.75">
+    <row r="104" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A104" s="113" t="s">
         <v>238</v>
       </c>
@@ -14292,7 +14301,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="105" spans="1:14" x14ac:dyDescent="0.75">
+    <row r="105" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A105" s="109" t="s">
         <v>233</v>
       </c>
@@ -14313,7 +14322,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="106" spans="1:14" x14ac:dyDescent="0.75">
+    <row r="106" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A106" t="s">
         <v>242</v>
       </c>
@@ -14336,7 +14345,7 @@
         <v>7.5</v>
       </c>
     </row>
-    <row r="107" spans="1:14" x14ac:dyDescent="0.75">
+    <row r="107" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A107" s="20" t="s">
         <v>243</v>
       </c>
@@ -14359,7 +14368,7 @@
         <v>4.9000000000000004</v>
       </c>
     </row>
-    <row r="108" spans="1:14" x14ac:dyDescent="0.75">
+    <row r="108" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A108" s="104" t="s">
         <v>244</v>
       </c>
@@ -14382,7 +14391,7 @@
         <v>-87</v>
       </c>
     </row>
-    <row r="109" spans="1:14" x14ac:dyDescent="0.75">
+    <row r="109" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A109" s="113" t="s">
         <v>245</v>
       </c>
@@ -14405,7 +14414,7 @@
         <v>920</v>
       </c>
     </row>
-    <row r="110" spans="1:14" x14ac:dyDescent="0.75">
+    <row r="110" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A110" s="113" t="s">
         <v>246</v>
       </c>
@@ -14428,17 +14437,17 @@
         <v>-71</v>
       </c>
     </row>
-    <row r="111" spans="1:14" x14ac:dyDescent="0.75">
+    <row r="111" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A111" s="113"/>
       <c r="B111" s="129"/>
     </row>
-    <row r="112" spans="1:14" x14ac:dyDescent="0.75">
+    <row r="112" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A112" s="109" t="s">
         <v>247</v>
       </c>
       <c r="B112" s="130"/>
     </row>
-    <row r="113" spans="1:24" x14ac:dyDescent="0.75">
+    <row r="113" spans="1:24" x14ac:dyDescent="0.45">
       <c r="A113" t="s">
         <v>248</v>
       </c>
@@ -14446,7 +14455,7 @@
         <v>0.85</v>
       </c>
     </row>
-    <row r="114" spans="1:24" x14ac:dyDescent="0.75">
+    <row r="114" spans="1:24" x14ac:dyDescent="0.45">
       <c r="A114" s="20" t="s">
         <v>249</v>
       </c>
@@ -14454,7 +14463,7 @@
         <v>0.42857142857142855</v>
       </c>
     </row>
-    <row r="115" spans="1:24" x14ac:dyDescent="0.75">
+    <row r="115" spans="1:24" x14ac:dyDescent="0.45">
       <c r="A115" t="s">
         <v>250</v>
       </c>
@@ -14462,7 +14471,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="116" spans="1:24" x14ac:dyDescent="0.75">
+    <row r="116" spans="1:24" x14ac:dyDescent="0.45">
       <c r="A116" t="s">
         <v>251</v>
       </c>
@@ -14475,7 +14484,7 @@
       <c r="R116" s="133"/>
       <c r="V116" s="133"/>
     </row>
-    <row r="117" spans="1:24" x14ac:dyDescent="0.75">
+    <row r="117" spans="1:24" x14ac:dyDescent="0.45">
       <c r="A117" t="s">
         <v>252</v>
       </c>
@@ -14488,7 +14497,7 @@
       <c r="R117" s="136"/>
       <c r="V117" s="136"/>
     </row>
-    <row r="118" spans="1:24" x14ac:dyDescent="0.75">
+    <row r="118" spans="1:24" x14ac:dyDescent="0.45">
       <c r="B118" s="137"/>
       <c r="C118" s="138"/>
       <c r="D118" s="139"/>
@@ -14508,7 +14517,7 @@
       <c r="W118" s="140"/>
       <c r="X118" s="139"/>
     </row>
-    <row r="119" spans="1:24" x14ac:dyDescent="0.75">
+    <row r="119" spans="1:24" x14ac:dyDescent="0.45">
       <c r="A119" t="s">
         <v>253</v>
       </c>
@@ -14531,7 +14540,7 @@
       <c r="W119" s="142"/>
       <c r="X119" s="143"/>
     </row>
-    <row r="120" spans="1:24" x14ac:dyDescent="0.75">
+    <row r="120" spans="1:24" x14ac:dyDescent="0.45">
       <c r="B120" s="144"/>
       <c r="C120" s="136"/>
       <c r="D120" s="145"/>
@@ -14551,7 +14560,7 @@
       <c r="W120" s="136"/>
       <c r="X120" s="145"/>
     </row>
-    <row r="121" spans="1:24" x14ac:dyDescent="0.75">
+    <row r="121" spans="1:24" x14ac:dyDescent="0.45">
       <c r="B121" s="144">
         <v>10</v>
       </c>
@@ -14583,7 +14592,7 @@
       <c r="W121" s="136"/>
       <c r="X121" s="145"/>
     </row>
-    <row r="122" spans="1:24" x14ac:dyDescent="0.75">
+    <row r="122" spans="1:24" x14ac:dyDescent="0.45">
       <c r="B122" s="144">
         <v>10</v>
       </c>
@@ -14615,7 +14624,7 @@
       <c r="W122" s="136"/>
       <c r="X122" s="145"/>
     </row>
-    <row r="123" spans="1:24" x14ac:dyDescent="0.75">
+    <row r="123" spans="1:24" x14ac:dyDescent="0.45">
       <c r="B123" s="144" t="s">
         <v>254</v>
       </c>
@@ -14671,7 +14680,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="124" spans="1:24" x14ac:dyDescent="0.75">
+    <row r="124" spans="1:24" x14ac:dyDescent="0.45">
       <c r="B124" s="144">
         <v>1990</v>
       </c>
@@ -14727,7 +14736,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="125" spans="1:24" x14ac:dyDescent="0.75">
+    <row r="125" spans="1:24" x14ac:dyDescent="0.45">
       <c r="B125" s="144">
         <v>1995</v>
       </c>
@@ -14783,7 +14792,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="126" spans="1:24" x14ac:dyDescent="0.75">
+    <row r="126" spans="1:24" x14ac:dyDescent="0.45">
       <c r="B126" s="149">
         <v>2000</v>
       </c>
@@ -14839,7 +14848,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="127" spans="1:24" x14ac:dyDescent="0.75">
+    <row r="127" spans="1:24" x14ac:dyDescent="0.45">
       <c r="B127">
         <v>2005</v>
       </c>
@@ -14895,7 +14904,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="128" spans="1:24" x14ac:dyDescent="0.75">
+    <row r="128" spans="1:24" x14ac:dyDescent="0.45">
       <c r="A128" s="20"/>
       <c r="B128">
         <v>2010</v>
@@ -14952,7 +14961,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="129" spans="1:24" x14ac:dyDescent="0.75">
+    <row r="129" spans="1:24" x14ac:dyDescent="0.45">
       <c r="A129" s="152"/>
       <c r="B129" s="153">
         <v>2015</v>
@@ -15010,7 +15019,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="130" spans="1:24" x14ac:dyDescent="0.75">
+    <row r="130" spans="1:24" x14ac:dyDescent="0.45">
       <c r="A130" s="155"/>
       <c r="B130" s="156">
         <v>2017</v>
@@ -15068,7 +15077,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="131" spans="1:24" x14ac:dyDescent="0.75">
+    <row r="131" spans="1:24" x14ac:dyDescent="0.45">
       <c r="A131" s="155"/>
       <c r="B131" s="159">
         <v>2020</v>
@@ -15082,7 +15091,7 @@
       <c r="E131" s="157"/>
       <c r="F131" s="160"/>
     </row>
-    <row r="132" spans="1:24" x14ac:dyDescent="0.75">
+    <row r="132" spans="1:24" x14ac:dyDescent="0.45">
       <c r="A132" s="155"/>
       <c r="B132" s="159"/>
       <c r="C132" s="159"/>
@@ -15090,7 +15099,7 @@
       <c r="E132" s="159"/>
       <c r="F132" s="160"/>
     </row>
-    <row r="133" spans="1:24" x14ac:dyDescent="0.75">
+    <row r="133" spans="1:24" x14ac:dyDescent="0.45">
       <c r="A133" s="155" t="s">
         <v>262</v>
       </c>
@@ -15100,7 +15109,7 @@
       <c r="E133" s="156"/>
       <c r="F133" s="158"/>
     </row>
-    <row r="134" spans="1:24" x14ac:dyDescent="0.75">
+    <row r="134" spans="1:24" x14ac:dyDescent="0.45">
       <c r="A134" s="161" t="s">
         <v>263</v>
       </c>
@@ -15120,7 +15129,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="135" spans="1:24" x14ac:dyDescent="0.75">
+    <row r="135" spans="1:24" x14ac:dyDescent="0.45">
       <c r="A135" t="s">
         <v>269</v>
       </c>
@@ -15140,7 +15149,7 @@
         <v>907184.74</v>
       </c>
     </row>
-    <row r="136" spans="1:24" x14ac:dyDescent="0.75">
+    <row r="136" spans="1:24" x14ac:dyDescent="0.45">
       <c r="A136" s="152" t="s">
         <v>270</v>
       </c>
@@ -15160,7 +15169,7 @@
         <v>907.18474000000003</v>
       </c>
     </row>
-    <row r="137" spans="1:24" x14ac:dyDescent="0.75">
+    <row r="137" spans="1:24" x14ac:dyDescent="0.45">
       <c r="A137" s="155" t="s">
         <v>271</v>
       </c>
@@ -15180,7 +15189,7 @@
         <v>0.90718474000000004</v>
       </c>
     </row>
-    <row r="138" spans="1:24" x14ac:dyDescent="0.75">
+    <row r="138" spans="1:24" x14ac:dyDescent="0.45">
       <c r="A138" s="155" t="s">
         <v>272</v>
       </c>
@@ -15200,7 +15209,7 @@
         <v>2000</v>
       </c>
     </row>
-    <row r="139" spans="1:24" x14ac:dyDescent="0.75">
+    <row r="139" spans="1:24" x14ac:dyDescent="0.45">
       <c r="A139" s="155" t="s">
         <v>273</v>
       </c>
@@ -15220,7 +15229,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="140" spans="1:24" x14ac:dyDescent="0.75">
+    <row r="140" spans="1:24" x14ac:dyDescent="0.45">
       <c r="A140" s="155"/>
       <c r="B140" s="136"/>
       <c r="C140" s="159"/>
@@ -15228,7 +15237,7 @@
       <c r="E140" s="156"/>
       <c r="F140" s="160"/>
     </row>
-    <row r="141" spans="1:24" x14ac:dyDescent="0.75">
+    <row r="141" spans="1:24" x14ac:dyDescent="0.45">
       <c r="A141" s="161" t="s">
         <v>274</v>
       </c>
@@ -15248,7 +15257,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="142" spans="1:24" x14ac:dyDescent="0.75">
+    <row r="142" spans="1:24" x14ac:dyDescent="0.45">
       <c r="A142" t="s">
         <v>280</v>
       </c>
@@ -15268,7 +15277,7 @@
         <v>2.8316846999999999E-2</v>
       </c>
     </row>
-    <row r="143" spans="1:24" x14ac:dyDescent="0.75">
+    <row r="143" spans="1:24" x14ac:dyDescent="0.45">
       <c r="A143" s="152" t="s">
         <v>281</v>
       </c>
@@ -15291,7 +15300,7 @@
       <c r="H143" s="153"/>
       <c r="I143" s="154"/>
     </row>
-    <row r="144" spans="1:24" x14ac:dyDescent="0.75">
+    <row r="144" spans="1:24" x14ac:dyDescent="0.45">
       <c r="A144" s="155" t="s">
         <v>282</v>
       </c>
@@ -15314,7 +15323,7 @@
       <c r="H144" s="156"/>
       <c r="I144" s="115"/>
     </row>
-    <row r="145" spans="1:9" x14ac:dyDescent="0.75">
+    <row r="145" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A145" s="155" t="s">
         <v>283</v>
       </c>
@@ -15337,7 +15346,7 @@
       <c r="H145" s="156"/>
       <c r="I145" s="115"/>
     </row>
-    <row r="146" spans="1:9" x14ac:dyDescent="0.75">
+    <row r="146" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A146" s="155" t="s">
         <v>284</v>
       </c>
@@ -15360,7 +15369,7 @@
       <c r="H146" s="156"/>
       <c r="I146" s="115"/>
     </row>
-    <row r="147" spans="1:9" x14ac:dyDescent="0.75">
+    <row r="147" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A147" s="155"/>
       <c r="B147" s="159"/>
       <c r="C147" s="157"/>
@@ -15371,7 +15380,7 @@
       <c r="H147" s="156"/>
       <c r="I147" s="115"/>
     </row>
-    <row r="148" spans="1:9" x14ac:dyDescent="0.75">
+    <row r="148" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A148" s="155" t="s">
         <v>285</v>
       </c>
@@ -15400,7 +15409,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="149" spans="1:9" x14ac:dyDescent="0.75">
+    <row r="149" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A149" s="155" t="s">
         <v>294</v>
       </c>
@@ -15429,7 +15438,7 @@
         <v>2684519.5376862194</v>
       </c>
     </row>
-    <row r="150" spans="1:9" x14ac:dyDescent="0.75">
+    <row r="150" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A150" s="155" t="s">
         <v>295</v>
       </c>
@@ -15458,7 +15467,7 @@
         <v>2684.5195376862198</v>
       </c>
     </row>
-    <row r="151" spans="1:9" x14ac:dyDescent="0.75">
+    <row r="151" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A151" s="161" t="s">
         <v>296</v>
       </c>
@@ -15487,7 +15496,7 @@
         <v>2.6845195376862194</v>
       </c>
     </row>
-    <row r="152" spans="1:9" x14ac:dyDescent="0.75">
+    <row r="152" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A152" t="s">
         <v>297</v>
       </c>
@@ -15516,7 +15525,7 @@
         <v>745.69987157950538</v>
       </c>
     </row>
-    <row r="153" spans="1:9" x14ac:dyDescent="0.75">
+    <row r="153" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A153" t="s">
         <v>298</v>
       </c>
@@ -15545,7 +15554,7 @@
         <v>0.74569987157950535</v>
       </c>
     </row>
-    <row r="154" spans="1:9" x14ac:dyDescent="0.75">
+    <row r="154" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A154" t="s">
         <v>299</v>
       </c>
@@ -15574,7 +15583,7 @@
         <v>2544.4335839531336</v>
       </c>
     </row>
-    <row r="155" spans="1:9" x14ac:dyDescent="0.75">
+    <row r="155" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A155" t="s">
         <v>300</v>
       </c>
@@ -15603,7 +15612,7 @@
         <v>2.5444335839531337E-3</v>
       </c>
     </row>
-    <row r="156" spans="1:9" x14ac:dyDescent="0.75">
+    <row r="156" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A156" t="s">
         <v>301</v>
       </c>
@@ -15632,7 +15641,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="158" spans="1:9" x14ac:dyDescent="0.75">
+    <row r="158" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A158" t="s">
         <v>413</v>
       </c>
@@ -15652,7 +15661,7 @@
         <v>418</v>
       </c>
     </row>
-    <row r="159" spans="1:9" x14ac:dyDescent="0.75">
+    <row r="159" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A159" t="s">
         <v>414</v>
       </c>
@@ -15672,7 +15681,7 @@
         <v>1609340</v>
       </c>
     </row>
-    <row r="160" spans="1:9" x14ac:dyDescent="0.75">
+    <row r="160" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A160" t="s">
         <v>415</v>
       </c>
@@ -15692,7 +15701,7 @@
         <v>1609.34</v>
       </c>
     </row>
-    <row r="161" spans="1:6" x14ac:dyDescent="0.75">
+    <row r="161" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A161" t="s">
         <v>416</v>
       </c>
@@ -15712,7 +15721,7 @@
         <v>1.60934</v>
       </c>
     </row>
-    <row r="162" spans="1:6" x14ac:dyDescent="0.75">
+    <row r="162" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A162" t="s">
         <v>417</v>
       </c>
@@ -15732,7 +15741,7 @@
         <v>5280</v>
       </c>
     </row>
-    <row r="163" spans="1:6" x14ac:dyDescent="0.75">
+    <row r="163" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A163" t="s">
         <v>418</v>
       </c>
@@ -15753,6 +15762,7 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="40" type="noConversion"/>
   <dataValidations count="5">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B100" xr:uid="{00000000-0002-0000-0200-000000000000}">
       <formula1>$D$100:$E$100</formula1>
@@ -15781,13 +15791,13 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AF22"/>
-  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
+  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="30.86328125" customWidth="1"/>
+    <col min="1" max="1" width="30.83203125" customWidth="1"/>
     <col min="2" max="32" width="10" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:32" x14ac:dyDescent="0.75">
+    <row r="1" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>404</v>
       </c>
@@ -15885,7 +15895,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:32" x14ac:dyDescent="0.75">
+    <row r="2" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>346</v>
       </c>
@@ -16014,7 +16024,7 @@
         <v>3412140000000</v>
       </c>
     </row>
-    <row r="3" spans="1:32" x14ac:dyDescent="0.75">
+    <row r="3" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>323</v>
       </c>
@@ -16143,7 +16153,7 @@
         <v>19887484000000</v>
       </c>
     </row>
-    <row r="4" spans="1:32" x14ac:dyDescent="0.75">
+    <row r="4" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>324</v>
       </c>
@@ -16272,7 +16282,7 @@
         <v>1036999999999999.9</v>
       </c>
     </row>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.75">
+    <row r="5" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
         <v>340</v>
       </c>
@@ -16401,7 +16411,7 @@
         <v>1000000000000</v>
       </c>
     </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.75">
+    <row r="6" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
         <v>341</v>
       </c>
@@ -16499,7 +16509,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.75">
+    <row r="7" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
         <v>342</v>
       </c>
@@ -16597,7 +16607,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.75">
+    <row r="8" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
         <v>343</v>
       </c>
@@ -16695,7 +16705,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:32" x14ac:dyDescent="0.75">
+    <row r="9" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
         <v>325</v>
       </c>
@@ -16824,7 +16834,7 @@
         <v>17906000000000</v>
       </c>
     </row>
-    <row r="10" spans="1:32" x14ac:dyDescent="0.75">
+    <row r="10" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
         <v>326</v>
       </c>
@@ -16953,7 +16963,7 @@
         <v>5810700000000</v>
       </c>
     </row>
-    <row r="11" spans="1:32" x14ac:dyDescent="0.75">
+    <row r="11" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
         <v>327</v>
       </c>
@@ -17082,7 +17092,7 @@
         <v>5810700000000</v>
       </c>
     </row>
-    <row r="12" spans="1:32" x14ac:dyDescent="0.75">
+    <row r="12" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
         <v>328</v>
       </c>
@@ -17211,7 +17221,7 @@
         <v>5810700000000</v>
       </c>
     </row>
-    <row r="13" spans="1:32" x14ac:dyDescent="0.75">
+    <row r="13" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
         <v>329</v>
       </c>
@@ -17340,7 +17350,7 @@
         <v>5810700000000</v>
       </c>
     </row>
-    <row r="14" spans="1:32" x14ac:dyDescent="0.75">
+    <row r="14" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
         <v>371</v>
       </c>
@@ -17469,7 +17479,7 @@
         <v>5810700000000</v>
       </c>
     </row>
-    <row r="15" spans="1:32" x14ac:dyDescent="0.75">
+    <row r="15" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
         <v>347</v>
       </c>
@@ -17598,7 +17608,7 @@
         <v>3412140000000</v>
       </c>
     </row>
-    <row r="16" spans="1:32" x14ac:dyDescent="0.75">
+    <row r="16" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
         <v>344</v>
       </c>
@@ -17696,7 +17706,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:32" x14ac:dyDescent="0.75">
+    <row r="17" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
         <v>330</v>
       </c>
@@ -17825,7 +17835,7 @@
         <v>12992301971719.6</v>
       </c>
     </row>
-    <row r="18" spans="1:32" x14ac:dyDescent="0.75">
+    <row r="18" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A18" t="s">
         <v>367</v>
       </c>
@@ -17954,7 +17964,7 @@
         <v>5810700000000</v>
       </c>
     </row>
-    <row r="19" spans="1:32" x14ac:dyDescent="0.75">
+    <row r="19" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A19" t="s">
         <v>368</v>
       </c>
@@ -18083,7 +18093,7 @@
         <v>5810700000000</v>
       </c>
     </row>
-    <row r="20" spans="1:32" x14ac:dyDescent="0.75">
+    <row r="20" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A20" t="s">
         <v>369</v>
       </c>
@@ -18212,7 +18222,7 @@
         <v>91410000000</v>
       </c>
     </row>
-    <row r="21" spans="1:32" x14ac:dyDescent="0.75">
+    <row r="21" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A21" t="s">
         <v>370</v>
       </c>
@@ -18341,7 +18351,7 @@
         <v>13583444584264.561</v>
       </c>
     </row>
-    <row r="22" spans="1:32" x14ac:dyDescent="0.75">
+    <row r="22" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A22" t="s">
         <v>366</v>
       </c>
@@ -18471,6 +18481,7 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="40" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -18481,13 +18492,13 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AI22"/>
-  <sheetFormatPr defaultColWidth="9.1328125" defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
+  <sheetFormatPr defaultColWidth="9.1640625" defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="30.86328125" customWidth="1"/>
+    <col min="1" max="1" width="30.83203125" customWidth="1"/>
     <col min="2" max="35" width="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="1" spans="1:35" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>405</v>
       </c>
@@ -18594,7 +18605,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="2" spans="1:35" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>352</v>
       </c>
@@ -18735,7 +18746,7 @@
         <v>3412140</v>
       </c>
     </row>
-    <row r="3" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="3" spans="1:35" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>323</v>
       </c>
@@ -18876,7 +18887,7 @@
         <v>19887484</v>
       </c>
     </row>
-    <row r="4" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="4" spans="1:35" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>324</v>
       </c>
@@ -19017,7 +19028,7 @@
         <v>1036999.9999999999</v>
       </c>
     </row>
-    <row r="5" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="5" spans="1:35" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
         <v>358</v>
       </c>
@@ -19158,7 +19169,7 @@
         <v>1000000</v>
       </c>
     </row>
-    <row r="6" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="6" spans="1:35" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
         <v>341</v>
       </c>
@@ -19265,7 +19276,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="7" spans="1:35" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
         <v>342</v>
       </c>
@@ -19372,7 +19383,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="8" spans="1:35" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
         <v>343</v>
       </c>
@@ -19479,7 +19490,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="9" spans="1:35" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
         <v>325</v>
       </c>
@@ -19620,7 +19631,7 @@
         <v>17906000</v>
       </c>
     </row>
-    <row r="10" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="10" spans="1:35" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
         <v>326</v>
       </c>
@@ -19761,7 +19772,7 @@
         <v>119596.09523809524</v>
       </c>
     </row>
-    <row r="11" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="11" spans="1:35" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
         <v>327</v>
       </c>
@@ -19902,7 +19913,7 @@
         <v>138690.47619047618</v>
       </c>
     </row>
-    <row r="12" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="12" spans="1:35" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
         <v>328</v>
       </c>
@@ -20043,7 +20054,7 @@
         <v>94981.738095238092</v>
       </c>
     </row>
-    <row r="13" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="13" spans="1:35" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
         <v>329</v>
       </c>
@@ -20184,7 +20195,7 @@
         <v>127595.23809523809</v>
       </c>
     </row>
-    <row r="14" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="14" spans="1:35" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
         <v>371</v>
       </c>
@@ -20325,7 +20336,7 @@
         <v>135000</v>
       </c>
     </row>
-    <row r="15" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="15" spans="1:35" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
         <v>353</v>
       </c>
@@ -20466,7 +20477,7 @@
         <v>3412140</v>
       </c>
     </row>
-    <row r="16" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="16" spans="1:35" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
         <v>344</v>
       </c>
@@ -20573,7 +20584,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="17" spans="1:35" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
         <v>330</v>
       </c>
@@ -20714,7 +20725,7 @@
         <v>12992301.9717196</v>
       </c>
     </row>
-    <row r="18" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="18" spans="1:35" x14ac:dyDescent="0.45">
       <c r="A18" t="s">
         <v>367</v>
       </c>
@@ -20855,7 +20866,7 @@
         <v>5810700</v>
       </c>
     </row>
-    <row r="19" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="19" spans="1:35" x14ac:dyDescent="0.45">
       <c r="A19" t="s">
         <v>368</v>
       </c>
@@ -20996,7 +21007,7 @@
         <v>5810700</v>
       </c>
     </row>
-    <row r="20" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="20" spans="1:35" x14ac:dyDescent="0.45">
       <c r="A20" t="s">
         <v>369</v>
       </c>
@@ -21137,7 +21148,7 @@
         <v>91410</v>
       </c>
     </row>
-    <row r="21" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="21" spans="1:35" x14ac:dyDescent="0.45">
       <c r="A21" t="s">
         <v>370</v>
       </c>
@@ -21278,7 +21289,7 @@
         <v>13583444.58426456</v>
       </c>
     </row>
-    <row r="22" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="22" spans="1:35" x14ac:dyDescent="0.45">
       <c r="A22" t="s">
         <v>366</v>
       </c>
@@ -21420,6 +21431,7 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="40" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -21430,13 +21442,13 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AI11"/>
-  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
+  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="38.26953125" customWidth="1"/>
+    <col min="1" max="1" width="38.25" customWidth="1"/>
     <col min="2" max="35" width="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="1" spans="1:35" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>403</v>
       </c>
@@ -21543,7 +21555,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="2" spans="1:35" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>310</v>
       </c>
@@ -21650,7 +21662,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="3" spans="1:35" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>311</v>
       </c>
@@ -21757,7 +21769,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="4" spans="1:35" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>318</v>
       </c>
@@ -21898,7 +21910,7 @@
         <v>119596.09523809524</v>
       </c>
     </row>
-    <row r="5" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="5" spans="1:35" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
         <v>319</v>
       </c>
@@ -22039,7 +22051,7 @@
         <v>138690.47619047618</v>
       </c>
     </row>
-    <row r="6" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="6" spans="1:35" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
         <v>312</v>
       </c>
@@ -22146,7 +22158,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="7" spans="1:35" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
         <v>313</v>
       </c>
@@ -22253,7 +22265,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="8" spans="1:35" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
         <v>320</v>
       </c>
@@ -22394,7 +22406,7 @@
         <v>135000</v>
       </c>
     </row>
-    <row r="9" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="9" spans="1:35" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
         <v>400</v>
       </c>
@@ -22501,7 +22513,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="10" spans="1:35" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
         <v>369</v>
       </c>
@@ -22608,7 +22620,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:35" x14ac:dyDescent="0.75">
+    <row r="11" spans="1:35" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
         <v>366</v>
       </c>
@@ -22716,6 +22728,7 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="40" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -22726,17 +22739,17 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
+  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="2" max="2" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B1" t="s">
         <v>402</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>299</v>
       </c>
@@ -22746,6 +22759,7 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="40" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -22756,26 +22770,198 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:A3"/>
-  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
+  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
         <v>430</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A2">
         <f>CONVERT(About!A77,"kg","lbm")*1000000000</f>
         <v>134510640026859.36</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A3" s="182"/>
     </row>
   </sheetData>
+  <phoneticPr fontId="40" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100E59C87379D9A4242BB3A95F198D6F941" ma:contentTypeVersion="4" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="07a235b40ffe2d9a960bde50f6511605">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="40f4d404-d193-41dc-bb72-733c1e774208" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="485fc8e6f691b86ce0aee9b7e82feca0" ns2:_="">
+    <xsd:import namespace="40f4d404-d193-41dc-bb72-733c1e774208"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="40f4d404-d193-41dc-bb72-733c1e774208" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="10" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="11" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{25CA2EA6-3DF9-458F-AC45-A601CE1FEBED}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{20C546D7-1456-4E60-AA76-522F02B15EFA}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{34D3769E-69F6-4F75-BF70-4CA07C14C65F}"/>
 </file>